--- a/sheet-template/GAMEOVER_시트_260905.xlsx
+++ b/sheet-template/GAMEOVER_시트_260905.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>주제는 인디 &amp; 기업입니다. 직접 만들어 본 사람과 지금 업계에서 일하는 사람이, 잘된 이야기보다 잘못된 이야기를 합니다.</t>
+          <t>주제는 인디 &amp; 기업입니다. 직접 만들어 본 사람과 지금 업계에서 일하는 사람이, 만들면서 실제로 겪은 이야기를 들려줍니다.</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -795,14 +795,7 @@
           <t>이런 발표가 아닙니다</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>포트폴리오·게임 소개 위주의 발표
-기술 입문 튜토리얼
-기업 채용 설명회 및 회사 홍보
-학술 논문 발표</t>
-        </is>
-      </c>
+      <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>한 줄에 하나씩</t>
@@ -832,11 +825,7 @@
           <t>발표 구성 덧말</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>사이를 어떻게 채울지는 연사에게 맡깁니다. 형식을 맞추는 것보다 실제로 겪은 이야기가 나오는 편이 중요합니다.</t>
-        </is>
-      </c>
+      <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>강연구성 표 아래 작은 글씨</t>
